--- a/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0002T0006Z000C1N95_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0002T0006Z000C1N95_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>15.40510834264238</v>
+        <v>2.503330105679386</v>
       </c>
       <c r="D2" t="n">
-        <v>14.12152790577402</v>
+        <v>2.294748284688279</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
